--- a/gte/nodes/LPC/compressor_blade_self_frequency.xlsx
+++ b/gte/nodes/LPC/compressor_blade_self_frequency.xlsx
@@ -543,58 +543,58 @@
         <v>1</v>
       </c>
       <c r="B3">
-        <v>202.30718952826419</v>
+        <v>186.80392542008428</v>
       </c>
       <c r="C3">
-        <v>1267.9290237863208</v>
+        <v>1170.7647135508719</v>
       </c>
       <c r="D3">
-        <v>3550.595117159301</v>
+        <v>3278.504866828162</v>
       </c>
       <c r="E3">
-        <v>6962.9638920305679</v>
+        <v>6429.3759931250343</v>
       </c>
       <c r="F3">
-        <v>11505.555499066404</v>
+        <v>10623.858382768778</v>
       </c>
       <c r="G3">
-        <v>17182.891548909924</v>
+        <v>15866.127145004515</v>
       </c>
       <c r="H3">
-        <v>1047.9939894072861</v>
+        <v>873.83711961735685</v>
       </c>
       <c r="I3">
-        <v>3143.9819682218586</v>
+        <v>2621.5113588520708</v>
       </c>
       <c r="J3">
-        <v>5239.96994703643</v>
+        <v>4369.185598086784</v>
       </c>
       <c r="K3">
-        <v>7335.9579258510021</v>
+        <v>6116.8598373214982</v>
       </c>
       <c r="L3">
-        <v>9431.9459046655757</v>
+        <v>7864.5340765562123</v>
       </c>
       <c r="M3">
-        <v>11527.933883480147</v>
+        <v>9612.2083157909256</v>
       </c>
       <c r="N3">
-        <v>2095.9879788145722</v>
+        <v>1747.6742392347137</v>
       </c>
       <c r="O3">
-        <v>4191.9759576291444</v>
+        <v>3495.3484784694274</v>
       </c>
       <c r="P3">
-        <v>6287.9639364437171</v>
+        <v>5243.0227177041415</v>
       </c>
       <c r="Q3">
-        <v>8383.9519152582889</v>
+        <v>6990.6969569388548</v>
       </c>
       <c r="R3">
-        <v>10479.939894072861</v>
+        <v>8738.371196173568</v>
       </c>
       <c r="S3">
-        <v>12575.927872887434</v>
+        <v>10486.045435408283</v>
       </c>
     </row>
     <row r="4" spans="1:19">
@@ -602,58 +602,58 @@
         <v>2</v>
       </c>
       <c r="B4">
-        <v>284.64718461494743</v>
+        <v>267.81851027389024</v>
       </c>
       <c r="C4">
-        <v>1783.9822092033567</v>
+        <v>1678.5110953065691</v>
       </c>
       <c r="D4">
-        <v>4995.70433539029</v>
+        <v>4700.3524545058308</v>
       </c>
       <c r="E4">
-        <v>9796.9235451473451</v>
+        <v>9217.7179713822479</v>
       </c>
       <c r="F4">
-        <v>16188.371692953242</v>
+        <v>15231.296232322135</v>
       </c>
       <c r="G4">
-        <v>24176.410706639053</v>
+        <v>22747.073040545336</v>
       </c>
       <c r="H4">
-        <v>1034.343954932933</v>
+        <v>862.45426871208826</v>
       </c>
       <c r="I4">
-        <v>3103.0318647987988</v>
+        <v>2587.3628061362647</v>
       </c>
       <c r="J4">
-        <v>5171.7197746646643</v>
+        <v>4312.271343560441</v>
       </c>
       <c r="K4">
-        <v>7240.4076845305308</v>
+        <v>6037.1798809846177</v>
       </c>
       <c r="L4">
-        <v>9309.0955943963963</v>
+        <v>7762.0884184087945</v>
       </c>
       <c r="M4">
-        <v>11377.783504262263</v>
+        <v>9486.99695583297</v>
       </c>
       <c r="N4">
-        <v>2068.687909865866</v>
+        <v>1724.9085374241765</v>
       </c>
       <c r="O4">
-        <v>4137.375819731732</v>
+        <v>3449.8170748483531</v>
       </c>
       <c r="P4">
-        <v>6206.0637295975976</v>
+        <v>5174.7256122725294</v>
       </c>
       <c r="Q4">
-        <v>8274.751639463464</v>
+        <v>6899.6341496967061</v>
       </c>
       <c r="R4">
-        <v>10343.439549329329</v>
+        <v>8624.542687120882</v>
       </c>
       <c r="S4">
-        <v>12412.127459195195</v>
+        <v>10349.451224545059</v>
       </c>
     </row>
     <row r="5" spans="1:19">
@@ -661,58 +661,58 @@
         <v>3</v>
       </c>
       <c r="B5">
-        <v>338.87179367355344</v>
+        <v>315.96448347947592</v>
       </c>
       <c r="C5">
-        <v>2123.8265607026287</v>
+        <v>1980.2585366513169</v>
       </c>
       <c r="D5">
-        <v>5947.3740837679688</v>
+        <v>5545.3390205949818</v>
       </c>
       <c r="E5">
-        <v>11663.214089813324</v>
+        <v>10874.795378066941</v>
       </c>
       <c r="F5">
-        <v>19272.217849848264</v>
+        <v>17969.43998324424</v>
       </c>
       <c r="G5">
-        <v>28781.959223766244</v>
+        <v>26836.334712546977</v>
       </c>
       <c r="H5">
-        <v>973.08696611185178</v>
+        <v>811.37772541411039</v>
       </c>
       <c r="I5">
-        <v>2919.2608983355549</v>
+        <v>2434.1331762423306</v>
       </c>
       <c r="J5">
-        <v>4865.4348305592584</v>
+        <v>4056.8886270705511</v>
       </c>
       <c r="K5">
-        <v>6811.608762782962</v>
+        <v>5679.6440778987717</v>
       </c>
       <c r="L5">
-        <v>8757.7826950066665</v>
+        <v>7302.3995287269927</v>
       </c>
       <c r="M5">
-        <v>10703.956627230369</v>
+        <v>8925.1549795552128</v>
       </c>
       <c r="N5">
-        <v>1946.1739322237036</v>
+        <v>1622.7554508282208</v>
       </c>
       <c r="O5">
-        <v>3892.3478644474071</v>
+        <v>3245.5109016564415</v>
       </c>
       <c r="P5">
-        <v>5838.52179667111</v>
+        <v>4868.2663524846612</v>
       </c>
       <c r="Q5">
-        <v>7784.6957288948142</v>
+        <v>6491.0218033128831</v>
       </c>
       <c r="R5">
-        <v>9730.8696611185169</v>
+        <v>8113.7772541411023</v>
       </c>
       <c r="S5">
-        <v>11677.04359334222</v>
+        <v>9736.5327049693224</v>
       </c>
     </row>
   </sheetData>
